--- a/template.xlsx
+++ b/template.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avclabs\Desktop\Python-Mercy\数据分析\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avclabs\Downloads\csv-to-xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12120"/>
+    <workbookView windowWidth="27945" windowHeight="11670"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="61">
   <si>
     <t>下载</t>
   </si>
@@ -157,6 +157,69 @@
   </si>
   <si>
     <t>Organic Social</t>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>10.18-10.24</t>
+  </si>
+  <si>
+    <t>10.11-10.17</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>1,295</t>
+  </si>
+  <si>
+    <t>1,345</t>
+  </si>
+  <si>
+    <t>-3.72%</t>
+  </si>
+  <si>
+    <t>下降</t>
+  </si>
+  <si>
+    <t>下载量</t>
+  </si>
+  <si>
+    <t>+5.83%</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>购买事件数</t>
+  </si>
+  <si>
+    <t>-19.33%</t>
+  </si>
+  <si>
+    <t>下载转化率</t>
+  </si>
+  <si>
+    <t>18.22%</t>
+  </si>
+  <si>
+    <t>16.58%</t>
+  </si>
+  <si>
+    <t>+1.64%</t>
+  </si>
+  <si>
+    <t>购买转化率</t>
+  </si>
+  <si>
+    <t>40.68%</t>
+  </si>
+  <si>
+    <t>53.36%</t>
+  </si>
+  <si>
+    <t>-12.69%</t>
   </si>
 </sst>
 </file>
@@ -201,10 +264,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -351,7 +412,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,12 +554,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -898,44 +953,44 @@
     <xf numFmtId="26" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="26" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1011,7 +1066,7 @@
     <xf numFmtId="26" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="26" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1029,6 +1084,7 @@
     <xf numFmtId="26" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="26" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1466,7 +1522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" ht="27" spans="1:18">
@@ -2932,18 +2988,113 @@
       <c r="J40" s="30"/>
       <c r="K40" s="30"/>
     </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
+    <row r="41" ht="15" spans="1:11">
+      <c r="A41" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="31" t="s">
+        <v>43</v>
+      </c>
       <c r="F41" s="30"/>
       <c r="G41" s="30"/>
       <c r="H41" s="30"/>
       <c r="I41" s="30"/>
       <c r="J41" s="30"/>
       <c r="K41" s="30"/>
+    </row>
+    <row r="42" ht="15" spans="1:11">
+      <c r="A42" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" ht="15" spans="1:11">
+      <c r="A43" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="31">
+        <v>236</v>
+      </c>
+      <c r="C43" s="31">
+        <v>223</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" ht="15" spans="1:11">
+      <c r="A44" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="31">
+        <v>96</v>
+      </c>
+      <c r="C44" s="31">
+        <v>119</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:11">
+      <c r="A45" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:11">
+      <c r="A46" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
